--- a/forms/app/chw_monthly_meeting.xlsx
+++ b/forms/app/chw_monthly_meeting.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20387"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20392"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BFE971-D608-428A-A71E-78C1AA6B8CED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE4E5A4-2488-4A72-820F-2412883C510D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="158">
   <si>
     <t>type</t>
   </si>
@@ -491,6 +491,12 @@
   <si>
     <t>Kazi ya mkutano wa mzewi itatokea  *_${c_formatted_task_date}_*.</t>
   </si>
+  <si>
+    <t>start</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
 </sst>
 </file>
 
@@ -499,7 +505,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dmmyyyyhm"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -534,13 +540,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -555,7 +578,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -582,6 +605,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -800,7 +826,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z1011"/>
+  <dimension ref="A1:Z1013"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1510,98 +1536,90 @@
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A21" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="13"/>
+      <c r="O21" s="13"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="13"/>
+      <c r="R21" s="13"/>
+      <c r="S21" s="13"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="6"/>
+    </row>
+    <row r="22" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A22" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="13"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="13"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="13"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6"/>
+    </row>
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B23" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C23" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4" t="s">
+      <c r="E23" s="4"/>
+      <c r="F23" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
-      <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="4"/>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="4"/>
-    </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -1627,13 +1645,13 @@
         <v>76</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
@@ -1660,13 +1678,17 @@
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="4" t="s">
-        <v>106</v>
+        <v>76</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
+      <c r="C25" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -1690,24 +1712,22 @@
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
-    <row r="26" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A26" s="3" t="s">
-        <v>13</v>
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="4" t="s">
+        <v>76</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>38</v>
+      <c r="B26" s="4" t="s">
+        <v>115</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>39</v>
+      <c r="C26" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
-      <c r="G26" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="G26" s="4"/>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -1728,22 +1748,17 @@
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
-    <row r="27" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A27" s="3" t="s">
-        <v>40</v>
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A27" s="4" t="s">
+        <v>106</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>41</v>
+      <c r="B27" s="4" t="s">
+        <v>108</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>120</v>
-      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
@@ -1767,16 +1782,22 @@
     </row>
     <row r="28" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A28" s="3" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+      <c r="C28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="G28" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -1797,13 +1818,22 @@
       <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
     </row>
-    <row r="29" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+    <row r="29" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+      <c r="A29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -1825,26 +1855,18 @@
       <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
     </row>
-    <row r="30" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A30" s="3" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>130</v>
-      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
       <c r="E30" s="4"/>
-      <c r="F30" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1865,33 +1887,17 @@
       <c r="Y30" s="4"/>
       <c r="Z30" s="4"/>
     </row>
-    <row r="31" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A31" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>120</v>
-      </c>
+    <row r="31" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
@@ -1911,31 +1917,27 @@
     </row>
     <row r="32" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A32" s="3" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>120</v>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3" t="s">
+        <v>45</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4" t="s">
-        <v>123</v>
+      <c r="G32" s="3" t="s">
+        <v>17</v>
       </c>
-      <c r="I32" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>125</v>
-      </c>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
@@ -1953,16 +1955,33 @@
       <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
     </row>
-    <row r="33" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="E33" s="4"/>
+    <row r="33" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+      <c r="A33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
@@ -1980,33 +1999,35 @@
       <c r="Y33" s="4"/>
       <c r="Z33" s="4"/>
     </row>
-    <row r="34" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A34" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>146</v>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>123</v>
       </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
+      <c r="I34" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="K34" s="4"/>
-      <c r="L34" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
@@ -2022,24 +2043,13 @@
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
-    <row r="35" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A35" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>147</v>
-      </c>
+    <row r="35" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
-      <c r="G35" s="3" t="s">
-        <v>57</v>
-      </c>
+      <c r="G35" s="4"/>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -2061,22 +2071,32 @@
       <c r="Z35" s="4"/>
     </row>
     <row r="36" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A36" s="4" t="s">
-        <v>18</v>
+      <c r="A36" s="3" t="s">
+        <v>51</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>1</v>
+      <c r="B36" s="3" t="s">
+        <v>52</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="C36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="G36" s="4"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
+      <c r="L36" s="3" t="s">
+        <v>54</v>
+      </c>
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
@@ -2092,18 +2112,24 @@
       <c r="Y36" s="4"/>
       <c r="Z36" s="4"/>
     </row>
-    <row r="37" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A37" s="3" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
+      <c r="C37" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
+      <c r="G37" s="3" t="s">
+        <v>57</v>
+      </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -2125,8 +2151,12 @@
       <c r="Z37" s="4"/>
     </row>
     <row r="38" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
+      <c r="A38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>1</v>
+      </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -2152,22 +2182,16 @@
       <c r="Y38" s="4"/>
       <c r="Z38" s="4"/>
     </row>
-    <row r="39" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A39" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
@@ -2191,25 +2215,13 @@
       <c r="Z39" s="4"/>
     </row>
     <row r="40" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A40" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>120</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
       <c r="F40" s="4"/>
-      <c r="G40" s="4" t="s">
-        <v>126</v>
-      </c>
+      <c r="G40" s="4"/>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -2230,18 +2242,18 @@
       <c r="Y40" s="4"/>
       <c r="Z40" s="4"/>
     </row>
-    <row r="41" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A41" s="3" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>120</v>
@@ -2270,16 +2282,24 @@
     </row>
     <row r="42" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A42" s="3" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
+      <c r="C42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
+      <c r="G42" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -2300,14 +2320,24 @@
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
     </row>
-    <row r="43" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
+    <row r="43" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+      <c r="A43" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="F43" s="4"/>
-      <c r="G43" s="3"/>
+      <c r="G43" s="4"/>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -2330,22 +2360,16 @@
     </row>
     <row r="44" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A44" s="3" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
-      <c r="C44" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>137</v>
-      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
       <c r="E44" s="4"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -2366,33 +2390,17 @@
       <c r="Y44" s="4"/>
       <c r="Z44" s="4"/>
     </row>
-    <row r="45" spans="1:26" ht="39" x14ac:dyDescent="0.6">
-      <c r="A45" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>120</v>
-      </c>
+    <row r="45" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>121</v>
-      </c>
+      <c r="G45" s="3"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
@@ -2412,16 +2420,22 @@
     </row>
     <row r="46" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A46" s="3" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C46" s="3"/>
-      <c r="D46" s="4"/>
+      <c r="C46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -2442,17 +2456,33 @@
       <c r="Y46" s="4"/>
       <c r="Z46" s="4"/>
     </row>
-    <row r="47" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
+    <row r="47" spans="1:26" ht="39" x14ac:dyDescent="0.6">
+      <c r="A47" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="4"/>
-      <c r="J47" s="4"/>
+      <c r="H47" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
@@ -2471,23 +2501,17 @@
       <c r="Z47" s="4"/>
     </row>
     <row r="48" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A48" s="5" t="s">
-        <v>13</v>
+      <c r="A48" s="3" t="s">
+        <v>34</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>73</v>
+      <c r="B48" s="3" t="s">
+        <v>66</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="E48" s="6"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
       <c r="F48" s="4"/>
-      <c r="G48" s="5" t="s">
-        <v>75</v>
-      </c>
+      <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -2508,26 +2532,14 @@
       <c r="Y48" s="4"/>
       <c r="Z48" s="4"/>
     </row>
-    <row r="49" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A49" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>140</v>
-      </c>
+    <row r="49" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>79</v>
-      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -2548,24 +2560,24 @@
       <c r="Y49" s="4"/>
       <c r="Z49" s="4"/>
     </row>
-    <row r="50" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A50" s="3" t="s">
-        <v>76</v>
+    <row r="50" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A50" s="5" t="s">
+        <v>13</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>80</v>
+      <c r="B50" s="5" t="s">
+        <v>73</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>81</v>
+      <c r="C50" s="5" t="s">
+        <v>74</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>81</v>
+      <c r="D50" s="6" t="s">
+        <v>139</v>
       </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4" t="s">
-        <v>45</v>
+      <c r="E50" s="6"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="5" t="s">
+        <v>75</v>
       </c>
-      <c r="G50" s="4"/>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -2586,21 +2598,23 @@
       <c r="Y50" s="4"/>
       <c r="Z50" s="4"/>
     </row>
-    <row r="51" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A51" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
+      <c r="F51" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="G51" s="3" t="s">
         <v>79</v>
       </c>
@@ -2624,26 +2638,28 @@
       <c r="Y51" s="4"/>
       <c r="Z51" s="4"/>
     </row>
-    <row r="52" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:26" ht="26" x14ac:dyDescent="0.6">
       <c r="A52" s="3" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
-      <c r="D52" s="4"/>
+      <c r="D52" s="4" t="s">
+        <v>81</v>
+      </c>
       <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
+      <c r="F52" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="G52" s="4"/>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
-      <c r="K52" s="4" t="s">
-        <v>148</v>
-      </c>
+      <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
@@ -2660,22 +2676,24 @@
       <c r="Y52" s="4"/>
       <c r="Z52" s="4"/>
     </row>
-    <row r="53" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:26" ht="13" x14ac:dyDescent="0.6">
       <c r="A53" s="3" t="s">
         <v>76</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
+      <c r="G53" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -2696,143 +2714,159 @@
       <c r="Y53" s="4"/>
       <c r="Z53" s="4"/>
     </row>
-    <row r="54" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A54" s="5" t="s">
+    <row r="54" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A54" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+    </row>
+    <row r="55" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+      <c r="A55" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+    </row>
+    <row r="56" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+      <c r="A56" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C56" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D56" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="5" t="s">
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
-      <c r="X54" s="6"/>
-      <c r="Y54" s="6"/>
-      <c r="Z54" s="6"/>
-    </row>
-    <row r="55" spans="1:26" ht="26" x14ac:dyDescent="0.6">
-      <c r="A55" s="5" t="s">
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6"/>
+      <c r="T56" s="6"/>
+      <c r="U56" s="6"/>
+      <c r="V56" s="6"/>
+      <c r="W56" s="6"/>
+      <c r="X56" s="6"/>
+      <c r="Y56" s="6"/>
+      <c r="Z56" s="6"/>
+    </row>
+    <row r="57" spans="1:26" ht="26" x14ac:dyDescent="0.6">
+      <c r="A57" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B57" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D57" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="6"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-    </row>
-    <row r="56" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A56" s="3" t="s">
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="6"/>
+      <c r="T57" s="6"/>
+      <c r="U57" s="6"/>
+      <c r="V57" s="6"/>
+      <c r="W57" s="6"/>
+      <c r="X57" s="6"/>
+      <c r="Y57" s="6"/>
+      <c r="Z57" s="6"/>
+    </row>
+    <row r="58" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A58" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B58" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
-    </row>
-    <row r="57" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
-      <c r="Z57" s="4"/>
-    </row>
-    <row r="58" spans="1:26" ht="13" x14ac:dyDescent="0.6">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -29541,6 +29575,62 @@
       <c r="X1011" s="4"/>
       <c r="Y1011" s="4"/>
       <c r="Z1011" s="4"/>
+    </row>
+    <row r="1012" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A1012" s="4"/>
+      <c r="B1012" s="4"/>
+      <c r="C1012" s="4"/>
+      <c r="D1012" s="4"/>
+      <c r="E1012" s="4"/>
+      <c r="F1012" s="4"/>
+      <c r="G1012" s="4"/>
+      <c r="H1012" s="4"/>
+      <c r="I1012" s="4"/>
+      <c r="J1012" s="4"/>
+      <c r="K1012" s="4"/>
+      <c r="L1012" s="4"/>
+      <c r="M1012" s="4"/>
+      <c r="N1012" s="4"/>
+      <c r="O1012" s="4"/>
+      <c r="P1012" s="4"/>
+      <c r="Q1012" s="4"/>
+      <c r="R1012" s="4"/>
+      <c r="S1012" s="4"/>
+      <c r="T1012" s="4"/>
+      <c r="U1012" s="4"/>
+      <c r="V1012" s="4"/>
+      <c r="W1012" s="4"/>
+      <c r="X1012" s="4"/>
+      <c r="Y1012" s="4"/>
+      <c r="Z1012" s="4"/>
+    </row>
+    <row r="1013" spans="1:26" ht="13" x14ac:dyDescent="0.6">
+      <c r="A1013" s="4"/>
+      <c r="B1013" s="4"/>
+      <c r="C1013" s="4"/>
+      <c r="D1013" s="4"/>
+      <c r="E1013" s="4"/>
+      <c r="F1013" s="4"/>
+      <c r="G1013" s="4"/>
+      <c r="H1013" s="4"/>
+      <c r="I1013" s="4"/>
+      <c r="J1013" s="4"/>
+      <c r="K1013" s="4"/>
+      <c r="L1013" s="4"/>
+      <c r="M1013" s="4"/>
+      <c r="N1013" s="4"/>
+      <c r="O1013" s="4"/>
+      <c r="P1013" s="4"/>
+      <c r="Q1013" s="4"/>
+      <c r="R1013" s="4"/>
+      <c r="S1013" s="4"/>
+      <c r="T1013" s="4"/>
+      <c r="U1013" s="4"/>
+      <c r="V1013" s="4"/>
+      <c r="W1013" s="4"/>
+      <c r="X1013" s="4"/>
+      <c r="Y1013" s="4"/>
+      <c r="Z1013" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29684,7 +29774,7 @@
       </c>
       <c r="C2" s="10">
         <f ca="1">NOW()</f>
-        <v>44785.42600983796</v>
+        <v>44901.53857650463</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>100</v>

--- a/forms/app/chw_monthly_meeting.xlsx
+++ b/forms/app/chw_monthly_meeting.xlsx
@@ -1,23 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20394"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\D-Tree\config-dtree\forms\app\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B0856DF-CEAF-4FF3-9C2F-BB25B53FAB36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7miuQCSr1fhRBPa9ou9ecu+ghG12kg=="/>
@@ -27,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="158">
   <si>
     <t>type</t>
   </si>
@@ -506,30 +497,30 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dmmyyyyhm"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
@@ -539,7 +530,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -549,58 +540,56 @@
     </fill>
   </fills>
   <borders count="2">
+    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -790,29 +779,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" customWidth="1"/>
-    <col min="3" max="3" width="47.42578125" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" customWidth="1"/>
-    <col min="5" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="58" customWidth="1"/>
-    <col min="12" max="26" width="18" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="18.0"/>
+    <col customWidth="1" min="2" max="2" width="28.88"/>
+    <col customWidth="1" min="3" max="3" width="47.38"/>
+    <col customWidth="1" min="4" max="4" width="60.75"/>
+    <col customWidth="1" min="5" max="10" width="18.0"/>
+    <col customWidth="1" min="11" max="11" width="58.0"/>
+    <col customWidth="1" min="12" max="26" width="18.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,7 +853,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -904,16 +891,14 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -938,16 +923,14 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -972,16 +955,14 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -1006,16 +987,14 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -1040,7 +1019,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -1076,7 +1055,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>23</v>
       </c>
@@ -1112,7 +1091,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -1148,7 +1127,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>23</v>
       </c>
@@ -1184,7 +1163,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -1220,7 +1199,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
@@ -1250,7 +1229,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>33</v>
       </c>
@@ -1280,7 +1259,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
@@ -1314,7 +1293,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -1348,7 +1327,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -1382,7 +1361,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>34</v>
       </c>
@@ -1416,7 +1395,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
@@ -1450,7 +1429,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>34</v>
       </c>
@@ -1484,7 +1463,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>34</v>
       </c>
@@ -1518,7 +1497,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>44</v>
       </c>
@@ -1550,7 +1529,7 @@
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
@@ -1582,7 +1561,7 @@
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
     </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>13</v>
       </c>
@@ -1622,7 +1601,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>51</v>
       </c>
@@ -1658,7 +1637,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>51</v>
       </c>
@@ -1694,7 +1673,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>51</v>
       </c>
@@ -1730,7 +1709,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -1762,7 +1741,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>13</v>
       </c>
@@ -1800,7 +1779,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>65</v>
       </c>
@@ -1837,7 +1816,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>33</v>
       </c>
@@ -1869,7 +1848,7 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -1897,7 +1876,7 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>13</v>
       </c>
@@ -1937,7 +1916,7 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>74</v>
       </c>
@@ -1981,7 +1960,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>74</v>
       </c>
@@ -2025,7 +2004,7 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -2052,7 +2031,7 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2" t="s">
         <v>85</v>
       </c>
@@ -2094,7 +2073,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2" t="s">
         <v>23</v>
       </c>
@@ -2132,16 +2111,14 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -2166,7 +2143,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2" t="s">
         <v>95</v>
       </c>
@@ -2198,7 +2175,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2226,7 +2203,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2" t="s">
         <v>96</v>
       </c>
@@ -2264,7 +2241,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>96</v>
       </c>
@@ -2304,7 +2281,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2" t="s">
         <v>96</v>
       </c>
@@ -2342,7 +2319,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>33</v>
       </c>
@@ -2374,7 +2351,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2402,7 +2379,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>13</v>
       </c>
@@ -2440,7 +2417,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>110</v>
       </c>
@@ -2484,7 +2461,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>33</v>
       </c>
@@ -2516,7 +2493,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2544,7 +2521,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>13</v>
       </c>
@@ -2582,7 +2559,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>51</v>
       </c>
@@ -2622,7 +2599,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>51</v>
       </c>
@@ -2660,7 +2637,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>51</v>
       </c>
@@ -2698,7 +2675,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>34</v>
       </c>
@@ -2734,7 +2711,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>51</v>
       </c>
@@ -2770,7 +2747,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>34</v>
       </c>
@@ -2808,7 +2785,7 @@
       <c r="Y56" s="4"/>
       <c r="Z56" s="4"/>
     </row>
-    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>51</v>
       </c>
@@ -2844,7 +2821,7 @@
       <c r="Y57" s="4"/>
       <c r="Z57" s="4"/>
     </row>
-    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>33</v>
       </c>
@@ -2876,7 +2853,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2904,7 +2881,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2932,7 +2909,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2960,7 +2937,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2988,7 +2965,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -3016,7 +2993,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -3044,7 +3021,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -3072,7 +3049,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -3100,7 +3077,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -3128,7 +3105,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -3156,7 +3133,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -3184,7 +3161,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -3212,7 +3189,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -3240,7 +3217,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -3268,7 +3245,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -3296,7 +3273,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -3324,7 +3301,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -3352,7 +3329,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3380,7 +3357,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3408,7 +3385,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3436,7 +3413,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3464,7 +3441,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3492,7 +3469,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3520,7 +3497,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -3548,7 +3525,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -3576,7 +3553,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -3604,7 +3581,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -3632,7 +3609,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -3660,7 +3637,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -3688,7 +3665,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -3716,7 +3693,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -3744,7 +3721,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -3772,7 +3749,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -3800,7 +3777,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -3828,7 +3805,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -3856,7 +3833,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -3884,7 +3861,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -3912,7 +3889,7 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -3940,7 +3917,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -3968,7 +3945,7 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -3996,7 +3973,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -4024,7 +4001,7 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
     </row>
-    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -4052,7 +4029,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -4080,7 +4057,7 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
     </row>
-    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -4108,7 +4085,7 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -4136,7 +4113,7 @@
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
     </row>
-    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -4164,7 +4141,7 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -4192,7 +4169,7 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
     </row>
-    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -4220,7 +4197,7 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -4248,7 +4225,7 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
     </row>
-    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -4276,7 +4253,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -4304,7 +4281,7 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -4332,7 +4309,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -4360,7 +4337,7 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
     </row>
-    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -4388,7 +4365,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -4416,7 +4393,7 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
     </row>
-    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -4444,7 +4421,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -4472,7 +4449,7 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
     </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -4500,7 +4477,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -4528,7 +4505,7 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
     </row>
-    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -4556,7 +4533,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4584,7 +4561,7 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
     </row>
-    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -4612,7 +4589,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4640,7 +4617,7 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
     </row>
-    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -4668,7 +4645,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -4696,7 +4673,7 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
     </row>
-    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -4724,7 +4701,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -4752,7 +4729,7 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
     </row>
-    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -4780,7 +4757,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -4808,7 +4785,7 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
     </row>
-    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -4836,7 +4813,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -4864,7 +4841,7 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
     </row>
-    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -4892,7 +4869,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -4920,7 +4897,7 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
     </row>
-    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -4948,7 +4925,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -4976,7 +4953,7 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
     </row>
-    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -5004,7 +4981,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -5032,7 +5009,7 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
     </row>
-    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -5060,7 +5037,7 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -5088,7 +5065,7 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
     </row>
-    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -5116,7 +5093,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -5144,7 +5121,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
     </row>
-    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -5172,7 +5149,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -5200,7 +5177,7 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
     </row>
-    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -5228,7 +5205,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -5256,7 +5233,7 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
     </row>
-    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -5284,7 +5261,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -5312,7 +5289,7 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -5340,7 +5317,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -5368,7 +5345,7 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -5396,7 +5373,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -5424,7 +5401,7 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
     </row>
-    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -5452,7 +5429,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -5480,7 +5457,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -5508,7 +5485,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -5536,7 +5513,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -5564,7 +5541,7 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -5592,7 +5569,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -5620,7 +5597,7 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -5648,7 +5625,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -5676,7 +5653,7 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -5704,7 +5681,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -5732,7 +5709,7 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -5760,7 +5737,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -5788,7 +5765,7 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -5816,7 +5793,7 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -5844,7 +5821,7 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -5872,7 +5849,7 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -5900,7 +5877,7 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -5928,7 +5905,7 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -5956,7 +5933,7 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
     </row>
-    <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -5984,7 +5961,7 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -6012,7 +5989,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -6040,7 +6017,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -6068,7 +6045,7 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
     </row>
-    <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -6096,7 +6073,7 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -6124,7 +6101,7 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -6152,7 +6129,7 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
     </row>
-    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -6180,7 +6157,7 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -6208,7 +6185,7 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
     </row>
-    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -6236,7 +6213,7 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -6264,7 +6241,7 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
     </row>
-    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -6292,7 +6269,7 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
     </row>
-    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -6320,7 +6297,7 @@
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
     </row>
-    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -6348,7 +6325,7 @@
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
     </row>
-    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -6376,7 +6353,7 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
     </row>
-    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -6404,7 +6381,7 @@
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
     </row>
-    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -6432,7 +6409,7 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
     </row>
-    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -6460,7 +6437,7 @@
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
     </row>
-    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -6488,7 +6465,7 @@
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
     </row>
-    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -6516,7 +6493,7 @@
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
     </row>
-    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -6544,7 +6521,7 @@
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
     </row>
-    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -6572,7 +6549,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -6600,7 +6577,7 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
     </row>
-    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -6628,7 +6605,7 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
     </row>
-    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -6656,7 +6633,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
-    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -6684,7 +6661,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
-    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -6712,7 +6689,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -6740,7 +6717,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -6768,7 +6745,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -6796,7 +6773,7 @@
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
     </row>
-    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -6824,7 +6801,7 @@
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
     </row>
-    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -6852,7 +6829,7 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
     </row>
-    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -6880,7 +6857,7 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
     </row>
-    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -6908,7 +6885,7 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
     </row>
-    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -6936,7 +6913,7 @@
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
     </row>
-    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -6964,7 +6941,7 @@
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
     </row>
-    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -6992,7 +6969,7 @@
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
     </row>
-    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -7020,7 +6997,7 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
     </row>
-    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -7048,7 +7025,7 @@
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
     </row>
-    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -7076,7 +7053,7 @@
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
     </row>
-    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -7104,7 +7081,7 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
     </row>
-    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -7132,7 +7109,7 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
     </row>
-    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -7160,7 +7137,7 @@
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
     </row>
-    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -7188,7 +7165,7 @@
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
     </row>
-    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -7216,7 +7193,7 @@
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
     </row>
-    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -7244,7 +7221,7 @@
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
     </row>
-    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -7272,7 +7249,7 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
     </row>
-    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -7300,7 +7277,7 @@
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
     </row>
-    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -7328,7 +7305,7 @@
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
     </row>
-    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -7356,7 +7333,7 @@
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
     </row>
-    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -7384,7 +7361,7 @@
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
     </row>
-    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -7412,7 +7389,7 @@
       <c r="Y220" s="2"/>
       <c r="Z220" s="2"/>
     </row>
-    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -7440,7 +7417,7 @@
       <c r="Y221" s="2"/>
       <c r="Z221" s="2"/>
     </row>
-    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -7468,7 +7445,7 @@
       <c r="Y222" s="2"/>
       <c r="Z222" s="2"/>
     </row>
-    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -7496,7 +7473,7 @@
       <c r="Y223" s="2"/>
       <c r="Z223" s="2"/>
     </row>
-    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -7524,7 +7501,7 @@
       <c r="Y224" s="2"/>
       <c r="Z224" s="2"/>
     </row>
-    <row r="225" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -7552,7 +7529,7 @@
       <c r="Y225" s="2"/>
       <c r="Z225" s="2"/>
     </row>
-    <row r="226" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -7580,7 +7557,7 @@
       <c r="Y226" s="2"/>
       <c r="Z226" s="2"/>
     </row>
-    <row r="227" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -7608,7 +7585,7 @@
       <c r="Y227" s="2"/>
       <c r="Z227" s="2"/>
     </row>
-    <row r="228" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -7636,7 +7613,7 @@
       <c r="Y228" s="2"/>
       <c r="Z228" s="2"/>
     </row>
-    <row r="229" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -7664,7 +7641,7 @@
       <c r="Y229" s="2"/>
       <c r="Z229" s="2"/>
     </row>
-    <row r="230" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -7692,7 +7669,7 @@
       <c r="Y230" s="2"/>
       <c r="Z230" s="2"/>
     </row>
-    <row r="231" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -7720,7 +7697,7 @@
       <c r="Y231" s="2"/>
       <c r="Z231" s="2"/>
     </row>
-    <row r="232" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -7748,7 +7725,7 @@
       <c r="Y232" s="2"/>
       <c r="Z232" s="2"/>
     </row>
-    <row r="233" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -7776,7 +7753,7 @@
       <c r="Y233" s="2"/>
       <c r="Z233" s="2"/>
     </row>
-    <row r="234" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -7804,7 +7781,7 @@
       <c r="Y234" s="2"/>
       <c r="Z234" s="2"/>
     </row>
-    <row r="235" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -7832,7 +7809,7 @@
       <c r="Y235" s="2"/>
       <c r="Z235" s="2"/>
     </row>
-    <row r="236" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -7860,7 +7837,7 @@
       <c r="Y236" s="2"/>
       <c r="Z236" s="2"/>
     </row>
-    <row r="237" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -7888,7 +7865,7 @@
       <c r="Y237" s="2"/>
       <c r="Z237" s="2"/>
     </row>
-    <row r="238" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -7916,7 +7893,7 @@
       <c r="Y238" s="2"/>
       <c r="Z238" s="2"/>
     </row>
-    <row r="239" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -7944,7 +7921,7 @@
       <c r="Y239" s="2"/>
       <c r="Z239" s="2"/>
     </row>
-    <row r="240" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -7972,7 +7949,7 @@
       <c r="Y240" s="2"/>
       <c r="Z240" s="2"/>
     </row>
-    <row r="241" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -8000,7 +7977,7 @@
       <c r="Y241" s="2"/>
       <c r="Z241" s="2"/>
     </row>
-    <row r="242" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -8028,7 +8005,7 @@
       <c r="Y242" s="2"/>
       <c r="Z242" s="2"/>
     </row>
-    <row r="243" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -8056,7 +8033,7 @@
       <c r="Y243" s="2"/>
       <c r="Z243" s="2"/>
     </row>
-    <row r="244" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -8084,7 +8061,7 @@
       <c r="Y244" s="2"/>
       <c r="Z244" s="2"/>
     </row>
-    <row r="245" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -8112,7 +8089,7 @@
       <c r="Y245" s="2"/>
       <c r="Z245" s="2"/>
     </row>
-    <row r="246" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -8140,7 +8117,7 @@
       <c r="Y246" s="2"/>
       <c r="Z246" s="2"/>
     </row>
-    <row r="247" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -8168,7 +8145,7 @@
       <c r="Y247" s="2"/>
       <c r="Z247" s="2"/>
     </row>
-    <row r="248" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -8196,7 +8173,7 @@
       <c r="Y248" s="2"/>
       <c r="Z248" s="2"/>
     </row>
-    <row r="249" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -8224,7 +8201,7 @@
       <c r="Y249" s="2"/>
       <c r="Z249" s="2"/>
     </row>
-    <row r="250" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -8252,7 +8229,7 @@
       <c r="Y250" s="2"/>
       <c r="Z250" s="2"/>
     </row>
-    <row r="251" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -8280,7 +8257,7 @@
       <c r="Y251" s="2"/>
       <c r="Z251" s="2"/>
     </row>
-    <row r="252" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -8308,7 +8285,7 @@
       <c r="Y252" s="2"/>
       <c r="Z252" s="2"/>
     </row>
-    <row r="253" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -8336,7 +8313,7 @@
       <c r="Y253" s="2"/>
       <c r="Z253" s="2"/>
     </row>
-    <row r="254" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -8364,7 +8341,7 @@
       <c r="Y254" s="2"/>
       <c r="Z254" s="2"/>
     </row>
-    <row r="255" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -8392,7 +8369,7 @@
       <c r="Y255" s="2"/>
       <c r="Z255" s="2"/>
     </row>
-    <row r="256" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -8420,7 +8397,7 @@
       <c r="Y256" s="2"/>
       <c r="Z256" s="2"/>
     </row>
-    <row r="257" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -8448,7 +8425,7 @@
       <c r="Y257" s="2"/>
       <c r="Z257" s="2"/>
     </row>
-    <row r="258" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -8476,766 +8453,768 @@
       <c r="Y258" s="2"/>
       <c r="Z258" s="2"/>
     </row>
-    <row r="259" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="6" width="12.5703125" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>139</v>
       </c>
@@ -9269,7 +9248,7 @@
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
     </row>
-    <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>140</v>
       </c>
@@ -9283,7 +9262,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>140</v>
       </c>
@@ -9297,1021 +9276,1023 @@
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="4" ht="15.75" customHeight="1"/>
+    <row r="5" ht="15.75" customHeight="1"/>
+    <row r="6" ht="15.75" customHeight="1"/>
+    <row r="7" ht="15.75" customHeight="1"/>
+    <row r="8" ht="15.75" customHeight="1"/>
+    <row r="9" ht="15.75" customHeight="1"/>
+    <row r="10" ht="15.75" customHeight="1"/>
+    <row r="11" ht="15.75" customHeight="1"/>
+    <row r="12" ht="15.75" customHeight="1"/>
+    <row r="13" ht="15.75" customHeight="1"/>
+    <row r="14" ht="15.75" customHeight="1"/>
+    <row r="15" ht="15.75" customHeight="1"/>
+    <row r="16" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="18" ht="15.75" customHeight="1"/>
+    <row r="19" ht="15.75" customHeight="1"/>
+    <row r="20" ht="15.75" customHeight="1"/>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="26" width="17.42578125" customWidth="1"/>
+    <col customWidth="1" min="1" max="26" width="17.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>147</v>
       </c>
@@ -10351,7 +10332,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>153</v>
       </c>
@@ -10359,8 +10340,8 @@
         <v>154</v>
       </c>
       <c r="C2" s="7">
-        <f ca="1">NOW()</f>
-        <v>44949.599346064817</v>
+        <f>NOW()</f>
+        <v>44949.04797</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>155</v>
@@ -10392,7 +10373,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -10420,7 +10401,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -10448,7 +10429,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -10476,7 +10457,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -10504,7 +10485,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -10532,7 +10513,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -10560,7 +10541,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -10588,7 +10569,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -10616,7 +10597,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -10644,7 +10625,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -10672,7 +10653,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -10700,7 +10681,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -10728,7 +10709,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -10756,7 +10737,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -10784,7 +10765,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -10812,7 +10793,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -10840,7 +10821,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -10868,7 +10849,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -10896,7 +10877,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -10924,7 +10905,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -10952,7 +10933,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -10980,7 +10961,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -11008,7 +10989,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -11036,7 +11017,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -11064,7 +11045,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -11092,7 +11073,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -11120,7 +11101,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -11148,7 +11129,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -11176,7 +11157,7 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -11204,7 +11185,7 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -11232,7 +11213,7 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -11260,7 +11241,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -11288,7 +11269,7 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -11316,7 +11297,7 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -11344,7 +11325,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -11372,7 +11353,7 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -11400,7 +11381,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -11428,7 +11409,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -11456,7 +11437,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -11484,7 +11465,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -11512,7 +11493,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -11540,7 +11521,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -11568,7 +11549,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -11596,7 +11577,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -11624,7 +11605,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -11652,7 +11633,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -11680,7 +11661,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -11708,7 +11689,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -11736,7 +11717,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -11764,7 +11745,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -11792,7 +11773,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -11820,7 +11801,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -11848,7 +11829,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -11876,7 +11857,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -11904,7 +11885,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -11932,7 +11913,7 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -11960,7 +11941,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -11988,7 +11969,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -12016,7 +11997,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -12044,7 +12025,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -12072,7 +12053,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -12100,7 +12081,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -12128,7 +12109,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -12156,7 +12137,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -12184,7 +12165,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -12212,7 +12193,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -12240,7 +12221,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -12268,7 +12249,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -12296,7 +12277,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -12324,7 +12305,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -12352,7 +12333,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -12380,7 +12361,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -12408,7 +12389,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -12436,7 +12417,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -12464,7 +12445,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -12492,7 +12473,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -12520,7 +12501,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -12548,7 +12529,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -12576,7 +12557,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -12604,7 +12585,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -12632,7 +12613,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -12660,7 +12641,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -12688,7 +12669,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -12716,7 +12697,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -12744,7 +12725,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -12772,7 +12753,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -12800,7 +12781,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -12828,7 +12809,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -12856,7 +12837,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -12884,7 +12865,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -12912,7 +12893,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -12940,7 +12921,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -12968,7 +12949,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -12996,7 +12977,7 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -13024,7 +13005,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -13052,7 +13033,7 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -13080,7 +13061,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -13108,7 +13089,7 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
     </row>
-    <row r="100" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -13136,7 +13117,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -13164,7 +13145,7 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
     </row>
-    <row r="102" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -13192,7 +13173,7 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -13220,7 +13201,7 @@
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
     </row>
-    <row r="104" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -13248,7 +13229,7 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -13276,7 +13257,7 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
     </row>
-    <row r="106" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -13304,7 +13285,7 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -13332,7 +13313,7 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
     </row>
-    <row r="108" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -13360,7 +13341,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -13388,7 +13369,7 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -13416,7 +13397,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -13444,7 +13425,7 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
     </row>
-    <row r="112" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -13472,7 +13453,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -13500,7 +13481,7 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
     </row>
-    <row r="114" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -13528,7 +13509,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -13556,7 +13537,7 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
     </row>
-    <row r="116" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -13584,7 +13565,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -13612,7 +13593,7 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
     </row>
-    <row r="118" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -13640,7 +13621,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -13668,7 +13649,7 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
     </row>
-    <row r="120" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -13696,7 +13677,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -13724,7 +13705,7 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
     </row>
-    <row r="122" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -13752,7 +13733,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -13780,7 +13761,7 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
     </row>
-    <row r="124" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -13808,7 +13789,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -13836,7 +13817,7 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
     </row>
-    <row r="126" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -13864,7 +13845,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -13892,7 +13873,7 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
     </row>
-    <row r="128" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -13920,7 +13901,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -13948,7 +13929,7 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
     </row>
-    <row r="130" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -13976,7 +13957,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -14004,7 +13985,7 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
     </row>
-    <row r="132" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -14032,7 +14013,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -14060,7 +14041,7 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
     </row>
-    <row r="134" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -14088,7 +14069,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -14116,7 +14097,7 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
     </row>
-    <row r="136" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -14144,7 +14125,7 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -14172,7 +14153,7 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
     </row>
-    <row r="138" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -14200,7 +14181,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -14228,7 +14209,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
     </row>
-    <row r="140" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -14256,7 +14237,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -14284,7 +14265,7 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
     </row>
-    <row r="142" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -14312,7 +14293,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -14340,7 +14321,7 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
     </row>
-    <row r="144" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -14368,7 +14349,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -14396,7 +14377,7 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -14424,7 +14405,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -14452,7 +14433,7 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -14480,7 +14461,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -14508,7 +14489,7 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
     </row>
-    <row r="150" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -14536,7 +14517,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -14564,7 +14545,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -14592,7 +14573,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -14620,7 +14601,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -14648,7 +14629,7 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -14676,7 +14657,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -14704,7 +14685,7 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -14732,7 +14713,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -14760,7 +14741,7 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -14788,7 +14769,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -14816,7 +14797,7 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
     </row>
-    <row r="161" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -14844,7 +14825,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -14872,7 +14853,7 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
     </row>
-    <row r="163" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -14900,7 +14881,7 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
     </row>
-    <row r="164" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -14928,7 +14909,7 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
     </row>
-    <row r="165" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -14956,7 +14937,7 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
     </row>
-    <row r="166" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -14984,7 +14965,7 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
     </row>
-    <row r="167" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -15012,7 +14993,7 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -15040,7 +15021,7 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
     </row>
-    <row r="169" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -15068,7 +15049,7 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -15096,7 +15077,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -15124,7 +15105,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -15152,7 +15133,7 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
     </row>
-    <row r="173" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -15180,7 +15161,7 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -15208,7 +15189,7 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -15236,7 +15217,7 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
     </row>
-    <row r="176" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -15264,7 +15245,7 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -15292,7 +15273,7 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
     </row>
-    <row r="178" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -15320,7 +15301,7 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -15348,7 +15329,7 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
     </row>
-    <row r="180" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -15376,7 +15357,7 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
     </row>
-    <row r="181" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -15404,7 +15385,7 @@
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
     </row>
-    <row r="182" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -15432,7 +15413,7 @@
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
     </row>
-    <row r="183" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -15460,7 +15441,7 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
     </row>
-    <row r="184" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -15488,7 +15469,7 @@
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
     </row>
-    <row r="185" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -15516,7 +15497,7 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
     </row>
-    <row r="186" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -15544,7 +15525,7 @@
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
     </row>
-    <row r="187" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -15572,7 +15553,7 @@
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
     </row>
-    <row r="188" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -15600,7 +15581,7 @@
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
     </row>
-    <row r="189" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -15628,7 +15609,7 @@
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
     </row>
-    <row r="190" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -15656,7 +15637,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
     </row>
-    <row r="191" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -15684,7 +15665,7 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
     </row>
-    <row r="192" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -15712,7 +15693,7 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
     </row>
-    <row r="193" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -15740,7 +15721,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
-    <row r="194" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -15768,7 +15749,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
-    <row r="195" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -15796,7 +15777,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -15824,7 +15805,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -15852,7 +15833,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -15880,7 +15861,7 @@
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
     </row>
-    <row r="199" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -15908,7 +15889,7 @@
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
     </row>
-    <row r="200" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -15936,7 +15917,7 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
     </row>
-    <row r="201" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -15964,7 +15945,7 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
     </row>
-    <row r="202" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -15992,7 +15973,7 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
     </row>
-    <row r="203" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -16020,7 +16001,7 @@
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
     </row>
-    <row r="204" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -16048,7 +16029,7 @@
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
     </row>
-    <row r="205" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -16076,7 +16057,7 @@
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
     </row>
-    <row r="206" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -16104,7 +16085,7 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
     </row>
-    <row r="207" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -16132,7 +16113,7 @@
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
     </row>
-    <row r="208" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -16160,7 +16141,7 @@
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
     </row>
-    <row r="209" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -16188,7 +16169,7 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
     </row>
-    <row r="210" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -16216,7 +16197,7 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
     </row>
-    <row r="211" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -16244,7 +16225,7 @@
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
     </row>
-    <row r="212" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -16272,7 +16253,7 @@
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
     </row>
-    <row r="213" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -16300,7 +16281,7 @@
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
     </row>
-    <row r="214" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -16328,7 +16309,7 @@
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
     </row>
-    <row r="215" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -16356,7 +16337,7 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
     </row>
-    <row r="216" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -16384,7 +16365,7 @@
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
     </row>
-    <row r="217" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -16412,7 +16393,7 @@
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
     </row>
-    <row r="218" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -16440,7 +16421,7 @@
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
     </row>
-    <row r="219" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -16468,7 +16449,7 @@
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
     </row>
-    <row r="220" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -16496,788 +16477,790 @@
       <c r="Y220" s="2"/>
       <c r="Z220" s="2"/>
     </row>
-    <row r="221" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>